--- a/excel_files/16.6.1.xlsx
+++ b/excel_files/16.6.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199CF9C4-E0D9-4388-BB10-7845700FC8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -136,13 +137,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00&quot;р.&quot;_-;\-* #,##0.00&quot;р.&quot;_-;_-* &quot;-&quot;??&quot;р.&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +160,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -223,6 +232,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,83 +272,101 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
+  <cellStyleXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="40" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="40" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="22">
-    <cellStyle name="Normal 4" xfId="3"/>
-    <cellStyle name="Normal_Sheet1" xfId="4"/>
-    <cellStyle name="Денежный 2" xfId="5"/>
+  <cellStyles count="26">
+    <cellStyle name="Normal 17" xfId="23" xr:uid="{8E9AD458-35AA-44A6-B938-AFF9989BEF8D}"/>
+    <cellStyle name="Normal 2" xfId="24" xr:uid="{FB5788A9-9625-4B30-AAC0-41A0D2A36A75}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal_Sheet1" xfId="4" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Денежный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="6"/>
-    <cellStyle name="Обычный 2 2" xfId="7"/>
-    <cellStyle name="Обычный 3" xfId="8"/>
-    <cellStyle name="Обычный 3 2" xfId="9"/>
-    <cellStyle name="Обычный 4" xfId="10"/>
-    <cellStyle name="Обычный 5" xfId="11"/>
-    <cellStyle name="Обычный 6" xfId="1"/>
-    <cellStyle name="Обычный 8" xfId="12"/>
-    <cellStyle name="Процентный 2" xfId="13"/>
-    <cellStyle name="Процентный 2 2" xfId="14"/>
-    <cellStyle name="Процентный 2 3" xfId="15"/>
-    <cellStyle name="Процентный 2 4" xfId="16"/>
-    <cellStyle name="Процентный 3" xfId="17"/>
-    <cellStyle name="Процентный 4" xfId="18"/>
-    <cellStyle name="Тысячи [0]_MESTBYD" xfId="19"/>
-    <cellStyle name="Тысячи_MESTBYD" xfId="20"/>
-    <cellStyle name="Финансовый 2" xfId="2"/>
-    <cellStyle name="Финансовый 2 2" xfId="21"/>
+    <cellStyle name="Обычный 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 4" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 5" xfId="11" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 5 2" xfId="25" xr:uid="{69428E7C-83E3-4D7C-8CD2-8897D687255F}"/>
+    <cellStyle name="Обычный 5 3" xfId="22" xr:uid="{632B56BD-EE32-418D-B589-950F19479A57}"/>
+    <cellStyle name="Обычный 6" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 8" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Процентный 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Процентный 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Процентный 2 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Процентный 2 4" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Процентный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Процентный 4" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Тысячи [0]_MESTBYD" xfId="19" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Тысячи_MESTBYD" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Финансовый 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Финансовый 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -343,9 +382,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -383,9 +422,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -420,7 +459,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -455,7 +494,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,15 +667,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.5703125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="66.75" customHeight="1">
+    <row r="1" spans="1:18" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -647,7 +686,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1">
+    <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>36</v>
       </c>
@@ -658,7 +697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:18" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -676,8 +715,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" thickBot="1">
+      <c r="R3" s="12"/>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -729,8 +769,11 @@
       <c r="Q4" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R4" s="13">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -740,8 +783,9 @@
       <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R5" s="10"/>
+    </row>
+    <row r="6" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -793,8 +837,11 @@
       <c r="Q6" s="1">
         <v>101.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R6" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -846,8 +893,11 @@
       <c r="Q7" s="1">
         <v>68.599999999999994</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R7" s="11">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -899,8 +949,11 @@
       <c r="Q8" s="1">
         <v>128.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R8" s="11">
+        <v>168.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -952,8 +1005,11 @@
       <c r="Q9" s="1">
         <v>227.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R9" s="11">
+        <v>196.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1005,8 +1061,11 @@
       <c r="Q10" s="1">
         <v>101.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="27" customHeight="1">
+      <c r="R10" s="11">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -1058,8 +1117,11 @@
       <c r="Q11" s="1">
         <v>130.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R11" s="11">
+        <v>115.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1111,8 +1173,11 @@
       <c r="Q12" s="1">
         <v>109.7</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickBot="1">
+      <c r="R12" s="11">
+        <v>107.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1164,8 +1229,11 @@
       <c r="Q13" s="4">
         <v>102</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="16.5" customHeight="1">
+      <c r="R13" s="12">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -1175,6 +1243,7 @@
       <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="R14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
